--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edubuas-my.sharepoint.com/personal/buckens_m_buas_nl/Documents/2C/Y2C-2425/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{A91E47EE-1B7B-4C21-94BB-219C34D1CD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE4174E9-6336-48BE-8495-A13DF4591228}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA4133C-8966-4A36-A2E1-D979A33EE2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
+    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -138,6 +138,46 @@
   <si>
     <t>Features used 
 (if applicable)</t>
+  </si>
+  <si>
+    <t>Naïve model</t>
+  </si>
+  <si>
+    <t>MultinomialNB from sklearn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go emotions dutch https://huggingface.co/datasets/joost6196/go_emotions_dutch/viewer/simplified?views%5B%5D=simplified_train </t>
+  </si>
+  <si>
+    <t>train = 57100 lines test = 1050 lines</t>
+  </si>
+  <si>
+    <t>TF-IDF Vectorization using tfidfVectorizer</t>
+  </si>
+  <si>
+    <t>not applicable</t>
+  </si>
+  <si>
+    <t>Hyper parameters for vectorizer
+max_features=7000,        # Keep top N most frequent words
+    ngram_range=(1, 2),       # (1,1) = unigrams, (1,2) = uni+bigrams
+    min_df=2,                 # Ignore words appearing in &lt; 2 documents
+    max_df=0.95,              # Ignore words appearing in &gt; 95% of docs
+    sublinear_tf=True,        # Apply log scaling to term frequency
+    use_idf=True,             # Use inverse document frequency
+    norm='l2'                 # Normalize vectors to unit length
+hyper parameters for model
+    alpha=1.0,                # Smoothing parameter (higher = more smoothing)
+    fit_prior=True</t>
+  </si>
+  <si>
+    <t>Koen Matthijssen 242817</t>
+  </si>
+  <si>
+    <t>the overall performance of the model can not be considered for our final pipeline. The evaluation metrics even after hyper parameter tuning is to low. After creating an cofusion matrix we found out that tme model was only predicting 2 classes. This is most likely because our dataset is skewed and the model tries to take adventige of this</t>
+  </si>
+  <si>
+    <t>none to speak of during this iteration</t>
   </si>
 </sst>
 </file>
@@ -810,31 +850,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A5CD43-FACF-4F92-BDE3-5E7B47D72998}">
   <dimension ref="B2:U51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="36" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="33.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="30.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.28515625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="20.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="33.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -856,7 +896,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="2:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
@@ -880,7 +920,7 @@
       <c r="T3" s="29"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -901,7 +941,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6"/>
       <c r="C5" s="18" t="s">
         <v>2</v>
@@ -924,7 +964,7 @@
       <c r="S5" s="18"/>
       <c r="T5" s="19"/>
     </row>
-    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
       <c r="C6" s="18" t="s">
         <v>3</v>
@@ -947,7 +987,7 @@
       <c r="S6" s="18"/>
       <c r="T6" s="19"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
       <c r="C7" s="18"/>
       <c r="D7" s="20"/>
@@ -968,7 +1008,7 @@
       <c r="S7" s="18"/>
       <c r="T7" s="19"/>
     </row>
-    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -989,7 +1029,7 @@
       <c r="S8" s="18"/>
       <c r="T8" s="19"/>
     </row>
-    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16"/>
       <c r="C9" s="30" t="s">
         <v>1</v>
@@ -1024,7 +1064,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
@@ -1079,30 +1119,58 @@
       <c r="S10" s="25"/>
       <c r="T10" s="26"/>
     </row>
-    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
         <v>1</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="C11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.38400000000000001</v>
+      </c>
       <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
+      <c r="P11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
+      <c r="S11" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="T11" s="11"/>
     </row>
-    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>2</v>
       </c>
@@ -1125,7 +1193,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="11"/>
     </row>
-    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="9">
         <v>3</v>
       </c>
@@ -1148,7 +1216,7 @@
       <c r="S13" s="10"/>
       <c r="T13" s="11"/>
     </row>
-    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="9">
         <v>4</v>
       </c>
@@ -1171,7 +1239,7 @@
       <c r="S14" s="10"/>
       <c r="T14" s="11"/>
     </row>
-    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -1194,7 +1262,7 @@
       <c r="S15" s="10"/>
       <c r="T15" s="11"/>
     </row>
-    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="9">
         <v>6</v>
       </c>
@@ -1217,7 +1285,7 @@
       <c r="S16" s="10"/>
       <c r="T16" s="11"/>
     </row>
-    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="9">
         <v>7</v>
       </c>
@@ -1240,7 +1308,7 @@
       <c r="S17" s="10"/>
       <c r="T17" s="11"/>
     </row>
-    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9">
         <v>8</v>
       </c>
@@ -1263,7 +1331,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="11"/>
     </row>
-    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="9">
         <v>9</v>
       </c>
@@ -1286,7 +1354,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="11"/>
     </row>
-    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -1309,7 +1377,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="11"/>
     </row>
-    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9">
         <v>11</v>
       </c>
@@ -1332,7 +1400,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="11"/>
     </row>
-    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9">
         <v>12</v>
       </c>
@@ -1355,7 +1423,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="11"/>
     </row>
-    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9">
         <v>13</v>
       </c>
@@ -1378,7 +1446,7 @@
       <c r="S23" s="10"/>
       <c r="T23" s="11"/>
     </row>
-    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9">
         <v>14</v>
       </c>
@@ -1401,7 +1469,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="11"/>
     </row>
-    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9">
         <v>15</v>
       </c>
@@ -1424,7 +1492,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="11"/>
     </row>
-    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9">
         <v>16</v>
       </c>
@@ -1447,7 +1515,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="11"/>
     </row>
-    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9">
         <v>17</v>
       </c>
@@ -1470,7 +1538,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="11"/>
     </row>
-    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="9">
         <v>18</v>
       </c>
@@ -1493,7 +1561,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="11"/>
     </row>
-    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="9">
         <v>19</v>
       </c>
@@ -1516,7 +1584,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="11"/>
     </row>
-    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9">
         <v>20</v>
       </c>
@@ -1539,7 +1607,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="11"/>
     </row>
-    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="9">
         <v>21</v>
       </c>
@@ -1562,7 +1630,7 @@
       <c r="S31" s="10"/>
       <c r="T31" s="11"/>
     </row>
-    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="9">
         <v>22</v>
       </c>
@@ -1585,7 +1653,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="11"/>
     </row>
-    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="9">
         <v>23</v>
       </c>
@@ -1608,7 +1676,7 @@
       <c r="S33" s="10"/>
       <c r="T33" s="11"/>
     </row>
-    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="9">
         <v>24</v>
       </c>
@@ -1631,7 +1699,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="11"/>
     </row>
-    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="9">
         <v>25</v>
       </c>
@@ -1654,7 +1722,7 @@
       <c r="S35" s="10"/>
       <c r="T35" s="11"/>
     </row>
-    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="9">
         <v>26</v>
       </c>
@@ -1677,7 +1745,7 @@
       <c r="S36" s="10"/>
       <c r="T36" s="11"/>
     </row>
-    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="9">
         <v>27</v>
       </c>
@@ -1700,7 +1768,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="11"/>
     </row>
-    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="9">
         <v>28</v>
       </c>
@@ -1723,7 +1791,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="11"/>
     </row>
-    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="9">
         <v>29</v>
       </c>
@@ -1746,7 +1814,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="11"/>
     </row>
-    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="9">
         <v>30</v>
       </c>
@@ -1769,7 +1837,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="11"/>
     </row>
-    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="9">
         <v>31</v>
       </c>
@@ -1792,7 +1860,7 @@
       <c r="S41" s="10"/>
       <c r="T41" s="11"/>
     </row>
-    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="9">
         <v>32</v>
       </c>
@@ -1815,7 +1883,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="9">
         <v>33</v>
       </c>
@@ -1838,7 +1906,7 @@
       <c r="S43" s="10"/>
       <c r="T43" s="11"/>
     </row>
-    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="9">
         <v>34</v>
       </c>
@@ -1861,7 +1929,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="11"/>
     </row>
-    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="9">
         <v>35</v>
       </c>
@@ -1884,7 +1952,7 @@
       <c r="S45" s="10"/>
       <c r="T45" s="11"/>
     </row>
-    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="9">
         <v>36</v>
       </c>
@@ -1907,7 +1975,7 @@
       <c r="S46" s="10"/>
       <c r="T46" s="11"/>
     </row>
-    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="9">
         <v>37</v>
       </c>
@@ -1930,7 +1998,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="11"/>
     </row>
-    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="9">
         <v>38</v>
       </c>
@@ -1953,7 +2021,7 @@
       <c r="S48" s="10"/>
       <c r="T48" s="11"/>
     </row>
-    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="9">
         <v>39</v>
       </c>
@@ -1976,7 +2044,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="11"/>
     </row>
-    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="12">
         <v>40</v>
       </c>
@@ -1999,7 +2067,7 @@
       <c r="S50" s="13"/>
       <c r="T50" s="14"/>
     </row>
-    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="15" t="s">
         <v>8</v>
       </c>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA4133C-8966-4A36-A2E1-D979A33EE2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354C7F89-0435-4EB9-A8F4-584B95F6C0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -178,6 +178,24 @@
   </si>
   <si>
     <t>none to speak of during this iteration</t>
+  </si>
+  <si>
+    <t>SVM model</t>
+  </si>
+  <si>
+    <t>LinearCSV from sklearn</t>
+  </si>
+  <si>
+    <t>train = 43410 lines test = 1050 lines</t>
+  </si>
+  <si>
+    <t>class_weight='balanced', max_iter=1000, C=0.1, loss='squared_hinge'</t>
+  </si>
+  <si>
+    <t>the simple approach does seem to be affective. It predicts more than 2 classes and with a f1 of 0.511 its outperforms the Naïve model by a lot</t>
+  </si>
+  <si>
+    <t>it gets a bad score on the less represented classes like disgust. The main issue is the amount of data we have on those classen</t>
   </si>
 </sst>
 </file>
@@ -1174,21 +1192,47 @@
       <c r="B12" s="9">
         <v>2</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="C12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.51100000000000001</v>
+      </c>
       <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="P12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
       <c r="T12" s="11"/>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354C7F89-0435-4EB9-A8F4-584B95F6C0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B5384E-176D-4509-8626-182F01D6B482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -1215,16 +1215,16 @@
         <v>41</v>
       </c>
       <c r="K12" s="10">
-        <v>0.54400000000000004</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="L12" s="10">
-        <v>0.51800000000000002</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="M12" s="10">
-        <v>0.54400000000000004</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="N12" s="10">
-        <v>0.51100000000000001</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10" t="s">

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B5384E-176D-4509-8626-182F01D6B482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C167D2CF-6A25-4CD1-BD43-16AC5A53C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -152,9 +152,6 @@
     <t>train = 57100 lines test = 1050 lines</t>
   </si>
   <si>
-    <t>TF-IDF Vectorization using tfidfVectorizer</t>
-  </si>
-  <si>
     <t>not applicable</t>
   </si>
   <si>
@@ -197,12 +194,24 @@
   <si>
     <t>it gets a bad score on the less represented classes like disgust. The main issue is the amount of data we have on those classen</t>
   </si>
+  <si>
+    <t>pre_trained_transformer</t>
+  </si>
+  <si>
+    <t>SamLowe/roberta-base-go_emotions</t>
+  </si>
+  <si>
+    <t>hf://datasets/google-research-datasets/go_emotions/</t>
+  </si>
+  <si>
+    <t>TF-IDF Vectorization using tfidfVectorizer and text</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +280,12 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -434,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -532,6 +547,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1155,13 +1173,13 @@
         <v>31</v>
       </c>
       <c r="H11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="J11" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>34</v>
       </c>
       <c r="K11" s="10">
         <v>0.38400000000000001</v>
@@ -1177,14 +1195,14 @@
       </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R11" s="10"/>
       <c r="S11" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T11" s="11"/>
     </row>
@@ -1193,26 +1211,26 @@
         <v>2</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>39</v>
-      </c>
       <c r="E12" s="10" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>41</v>
       </c>
       <c r="K12" s="10">
         <v>0.55800000000000005</v>
@@ -1228,10 +1246,10 @@
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q12" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="Q12" s="10" t="s">
-        <v>43</v>
       </c>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
@@ -1241,13 +1259,25 @@
       <c r="B13" s="9">
         <v>3</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C167D2CF-6A25-4CD1-BD43-16AC5A53C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC220CA-716D-4FAB-A816-689B479F9B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
+    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -195,9 +195,6 @@
     <t>it gets a bad score on the less represented classes like disgust. The main issue is the amount of data we have on those classen</t>
   </si>
   <si>
-    <t>pre_trained_transformer</t>
-  </si>
-  <si>
     <t>SamLowe/roberta-base-go_emotions</t>
   </si>
   <si>
@@ -205,13 +202,42 @@
   </si>
   <si>
     <t>TF-IDF Vectorization using tfidfVectorizer and text</t>
+  </si>
+  <si>
+    <t>num_train_epochs=3,
+    per_device_train_batch_size=16,  
+    per_device_eval_batch_size=32,
+    learning_rate=2e-5,
+    warmup_steps=500,
+    logging_steps=100,
+    eval_strategy="epoch",
+    save_strategy="epoch",
+    load_best_model_at_end=True,
+    metric_for_best_model="f1",
+    greater_is_better=True,
+    fp16=True,
+    report_to="none",
+    remove_unused_columns=False,  
+    dataloader_drop_last=False</t>
+  </si>
+  <si>
+    <t>pre_trained_transformer_finetuned</t>
+  </si>
+  <si>
+    <t>the main weakness of this model is that when finetuning I introduced my skewed training data to the model. This lead to the model getting a slightly worse performance then before the finetuning. We tried to combat this by using different parameters for our model and changing the base model. eventually we got the performance really close to just the base model performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The finetuning approach had several important strengths that initially made it promising for my emotion classification task. It allowed me to directly adapt the model to my specific 7 emotion categories rather than relying on arbitrary mappings, which meant the model could learn the exact patterns that distinguish my emotion definitions. The finetuning process leveraged transfer learning effectively, keeping the pre-trained language understanding from RoBERTa while only adjusting the classification head for my task. This meant I didn't need to train from scratch, saving computational resources and time. The approach also gave me full control over the training process, allowing me to adjust hyperparameters, implement class weighting for imbalanced data, and monitor detailed metrics during training. When evaluated on data with the same distribution as training, the finetuned model achieved strong performance around 0.78 F1 score, demonstrating it had successfully learned the emotion patterns. </t>
+  </si>
+  <si>
+    <t>we finetuned the model on our training data.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,12 +306,6 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -449,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -547,9 +567,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1173,7 +1190,7 @@
         <v>31</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>32</v>
@@ -1217,14 +1234,14 @@
         <v>38</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10" t="s">
         <v>39</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>32</v>
@@ -1233,16 +1250,16 @@
         <v>40</v>
       </c>
       <c r="K12" s="10">
-        <v>0.55800000000000005</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="L12" s="10">
-        <v>0.53100000000000003</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="M12" s="10">
-        <v>0.55800000000000005</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="N12" s="10">
-        <v>0.52400000000000002</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10" t="s">
@@ -1260,32 +1277,48 @@
         <v>3</v>
       </c>
       <c r="C13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="34"/>
+      <c r="F13" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="G13" s="10" t="s">
         <v>39</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="J13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0.7994</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0.79969999999999997</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0.7994</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.78029999999999999</v>
+      </c>
       <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
+      <c r="P13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>48</v>
+      </c>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
       <c r="T13" s="11"/>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC220CA-716D-4FAB-A816-689B479F9B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7606724-4C26-475A-BF44-40D67EF6222A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
@@ -1199,16 +1199,16 @@
         <v>33</v>
       </c>
       <c r="K11" s="10">
-        <v>0.38400000000000001</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="L11" s="10">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="M11" s="10">
-        <v>0.38400000000000001</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="N11" s="10">
-        <v>0.38400000000000001</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10" t="s">

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7606724-4C26-475A-BF44-40D67EF6222A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908665AF-B9F1-4051-894E-E8488C1E31EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908665AF-B9F1-4051-894E-E8488C1E31EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CA6972-B99C-422E-BA05-B5583382CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -231,6 +231,81 @@
   </si>
   <si>
     <t>we finetuned the model on our training data.</t>
+  </si>
+  <si>
+    <t>0.476</t>
+  </si>
+  <si>
+    <t>0.414</t>
+  </si>
+  <si>
+    <t>0.412</t>
+  </si>
+  <si>
+    <t>Bidirectional LSTM</t>
+  </si>
+  <si>
+    <t>dropout=0.5, max_vocab_size=5000, Max_len = 128, batch_size=32, learning_rate 1e-3</t>
+  </si>
+  <si>
+    <t>TF-IDF Vectorization using tfidfVectorizer and tekst, POS_Tags, Embeddings, Sentiment_Score</t>
+  </si>
+  <si>
+    <t>train=5000 lines, test = 1042</t>
+  </si>
+  <si>
+    <t>Go emotion english</t>
+  </si>
+  <si>
+    <t>String evaluation to fix strings to python objects, renaming some columns</t>
+  </si>
+  <si>
+    <t>0.503</t>
+  </si>
+  <si>
+    <t>0.365</t>
+  </si>
+  <si>
+    <t>0.421</t>
+  </si>
+  <si>
+    <t>Normalisation of values using standardscaler</t>
+  </si>
+  <si>
+    <t>Torch, scikitlearn</t>
+  </si>
+  <si>
+    <t>Quick training</t>
+  </si>
+  <si>
+    <t>Bad inference and results</t>
+  </si>
+  <si>
+    <t>0.482</t>
+  </si>
+  <si>
+    <t>0.446</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Stacked bidirectional LSTM</t>
+  </si>
+  <si>
+    <t>Nick Belterman</t>
+  </si>
+  <si>
+    <t>RNN</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>0.45</t>
   </si>
 </sst>
 </file>
@@ -903,31 +978,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A5CD43-FACF-4F92-BDE3-5E7B47D72998}">
   <dimension ref="B2:U51"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="6.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="6.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="36" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="33.109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="30.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.44140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.33203125" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.109375" style="1"/>
+    <col min="9" max="9" width="20.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="33.140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.28515625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.28515625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:21" ht="24" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -949,7 +1024,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:21" ht="24" x14ac:dyDescent="0.4">
       <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
@@ -973,7 +1048,7 @@
       <c r="T3" s="29"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -994,7 +1069,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6"/>
       <c r="C5" s="18" t="s">
         <v>2</v>
@@ -1017,7 +1092,7 @@
       <c r="S5" s="18"/>
       <c r="T5" s="19"/>
     </row>
-    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
       <c r="C6" s="18" t="s">
         <v>3</v>
@@ -1040,7 +1115,7 @@
       <c r="S6" s="18"/>
       <c r="T6" s="19"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="6"/>
       <c r="C7" s="18"/>
       <c r="D7" s="20"/>
@@ -1061,7 +1136,7 @@
       <c r="S7" s="18"/>
       <c r="T7" s="19"/>
     </row>
-    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -1082,7 +1157,7 @@
       <c r="S8" s="18"/>
       <c r="T8" s="19"/>
     </row>
-    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
       <c r="C9" s="30" t="s">
         <v>1</v>
@@ -1117,7 +1192,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
@@ -1172,7 +1247,7 @@
       <c r="S10" s="25"/>
       <c r="T10" s="26"/>
     </row>
-    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>1</v>
       </c>
@@ -1223,7 +1298,7 @@
       </c>
       <c r="T11" s="11"/>
     </row>
-    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9">
         <v>2</v>
       </c>
@@ -1272,7 +1347,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="11"/>
     </row>
-    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>3</v>
       </c>
@@ -1323,91 +1398,189 @@
       <c r="S13" s="10"/>
       <c r="T13" s="11"/>
     </row>
-    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9">
         <v>4</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="C14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="J14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
+      <c r="P14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
+      <c r="S14" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="T14" s="11"/>
     </row>
-    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9">
         <v>5</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="C15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="F15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
+      <c r="J15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
+      <c r="P15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
+      <c r="S15" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="T15" s="11"/>
     </row>
-    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9">
         <v>6</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="F16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="J16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
+      <c r="P16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
+      <c r="S16" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="T16" s="11"/>
     </row>
-    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9">
         <v>7</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="C17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="F17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="J17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
@@ -1415,7 +1588,7 @@
       <c r="S17" s="10"/>
       <c r="T17" s="11"/>
     </row>
-    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9">
         <v>8</v>
       </c>
@@ -1438,7 +1611,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="11"/>
     </row>
-    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="9">
         <v>9</v>
       </c>
@@ -1461,7 +1634,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="11"/>
     </row>
-    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -1484,7 +1657,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="11"/>
     </row>
-    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="9">
         <v>11</v>
       </c>
@@ -1507,7 +1680,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="11"/>
     </row>
-    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9">
         <v>12</v>
       </c>
@@ -1530,7 +1703,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="11"/>
     </row>
-    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9">
         <v>13</v>
       </c>
@@ -1553,7 +1726,7 @@
       <c r="S23" s="10"/>
       <c r="T23" s="11"/>
     </row>
-    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="9">
         <v>14</v>
       </c>
@@ -1576,7 +1749,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="11"/>
     </row>
-    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="9">
         <v>15</v>
       </c>
@@ -1599,7 +1772,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="11"/>
     </row>
-    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9">
         <v>16</v>
       </c>
@@ -1622,7 +1795,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="11"/>
     </row>
-    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="9">
         <v>17</v>
       </c>
@@ -1645,7 +1818,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="11"/>
     </row>
-    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="9">
         <v>18</v>
       </c>
@@ -1668,7 +1841,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="11"/>
     </row>
-    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="9">
         <v>19</v>
       </c>
@@ -1691,7 +1864,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="11"/>
     </row>
-    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="9">
         <v>20</v>
       </c>
@@ -1714,7 +1887,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="11"/>
     </row>
-    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9">
         <v>21</v>
       </c>
@@ -1737,7 +1910,7 @@
       <c r="S31" s="10"/>
       <c r="T31" s="11"/>
     </row>
-    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="9">
         <v>22</v>
       </c>
@@ -1760,7 +1933,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="11"/>
     </row>
-    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="9">
         <v>23</v>
       </c>
@@ -1783,7 +1956,7 @@
       <c r="S33" s="10"/>
       <c r="T33" s="11"/>
     </row>
-    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="9">
         <v>24</v>
       </c>
@@ -1806,7 +1979,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="11"/>
     </row>
-    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="9">
         <v>25</v>
       </c>
@@ -1829,7 +2002,7 @@
       <c r="S35" s="10"/>
       <c r="T35" s="11"/>
     </row>
-    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="9">
         <v>26</v>
       </c>
@@ -1852,7 +2025,7 @@
       <c r="S36" s="10"/>
       <c r="T36" s="11"/>
     </row>
-    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="9">
         <v>27</v>
       </c>
@@ -1875,7 +2048,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="11"/>
     </row>
-    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="9">
         <v>28</v>
       </c>
@@ -1898,7 +2071,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="11"/>
     </row>
-    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="9">
         <v>29</v>
       </c>
@@ -1921,7 +2094,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="11"/>
     </row>
-    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="9">
         <v>30</v>
       </c>
@@ -1944,7 +2117,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="11"/>
     </row>
-    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="9">
         <v>31</v>
       </c>
@@ -1967,7 +2140,7 @@
       <c r="S41" s="10"/>
       <c r="T41" s="11"/>
     </row>
-    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="9">
         <v>32</v>
       </c>
@@ -1990,7 +2163,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="9">
         <v>33</v>
       </c>
@@ -2013,7 +2186,7 @@
       <c r="S43" s="10"/>
       <c r="T43" s="11"/>
     </row>
-    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="9">
         <v>34</v>
       </c>
@@ -2036,7 +2209,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="11"/>
     </row>
-    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="9">
         <v>35</v>
       </c>
@@ -2059,7 +2232,7 @@
       <c r="S45" s="10"/>
       <c r="T45" s="11"/>
     </row>
-    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="9">
         <v>36</v>
       </c>
@@ -2082,7 +2255,7 @@
       <c r="S46" s="10"/>
       <c r="T46" s="11"/>
     </row>
-    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="9">
         <v>37</v>
       </c>
@@ -2105,7 +2278,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="11"/>
     </row>
-    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="9">
         <v>38</v>
       </c>
@@ -2128,7 +2301,7 @@
       <c r="S48" s="10"/>
       <c r="T48" s="11"/>
     </row>
-    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="9">
         <v>39</v>
       </c>
@@ -2151,7 +2324,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="11"/>
     </row>
-    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="12">
         <v>40</v>
       </c>
@@ -2174,7 +2347,7 @@
       <c r="S50" s="13"/>
       <c r="T50" s="14"/>
     </row>
-    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="15" t="s">
         <v>8</v>
       </c>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CA6972-B99C-422E-BA05-B5583382CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCA5980-FCF3-4640-8DEE-E54CAB095FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCA5980-FCF3-4640-8DEE-E54CAB095FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D9459A-0008-4BEA-A572-8801801A8DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -307,12 +307,27 @@
   <si>
     <t>0.45</t>
   </si>
+  <si>
+    <t>link to git</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/blob/main/nlp_cia/task%206/SVM.ipynb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/blob/main/nlp_cia/task%206/naive.ipynb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/blob/main/nlp_cia/task%206/pretrained_transformer_model.ipynb  </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,6 +396,14 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -541,10 +564,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -643,8 +667,12 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -978,31 +1006,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A5CD43-FACF-4F92-BDE3-5E7B47D72998}">
   <dimension ref="B2:U51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="36" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="33.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="30.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.28515625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="20.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="33.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1024,7 +1052,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="2:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1076,7 @@
       <c r="T3" s="29"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -1069,7 +1097,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6"/>
       <c r="C5" s="18" t="s">
         <v>2</v>
@@ -1092,7 +1120,7 @@
       <c r="S5" s="18"/>
       <c r="T5" s="19"/>
     </row>
-    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
       <c r="C6" s="18" t="s">
         <v>3</v>
@@ -1115,7 +1143,7 @@
       <c r="S6" s="18"/>
       <c r="T6" s="19"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
       <c r="C7" s="18"/>
       <c r="D7" s="20"/>
@@ -1136,7 +1164,7 @@
       <c r="S7" s="18"/>
       <c r="T7" s="19"/>
     </row>
-    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -1157,7 +1185,7 @@
       <c r="S8" s="18"/>
       <c r="T8" s="19"/>
     </row>
-    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16"/>
       <c r="C9" s="30" t="s">
         <v>1</v>
@@ -1192,7 +1220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
@@ -1244,10 +1272,14 @@
       <c r="R10" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-    </row>
-    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S10" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="T10" s="26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
         <v>1</v>
       </c>
@@ -1296,9 +1328,11 @@
       <c r="S11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="T11" s="11"/>
-    </row>
-    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T11" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>2</v>
       </c>
@@ -1344,10 +1378,14 @@
         <v>42</v>
       </c>
       <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="11"/>
-    </row>
-    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="9">
         <v>3</v>
       </c>
@@ -1395,10 +1433,14 @@
         <v>48</v>
       </c>
       <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="11"/>
-    </row>
-    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="9">
         <v>4</v>
       </c>
@@ -1449,7 +1491,7 @@
       </c>
       <c r="T14" s="11"/>
     </row>
-    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -1498,7 +1540,7 @@
       </c>
       <c r="T15" s="11"/>
     </row>
-    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="9">
         <v>6</v>
       </c>
@@ -1545,7 +1587,7 @@
       </c>
       <c r="T16" s="11"/>
     </row>
-    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="9">
         <v>7</v>
       </c>
@@ -1585,10 +1627,12 @@
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
+      <c r="S17" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="T17" s="11"/>
     </row>
-    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9">
         <v>8</v>
       </c>
@@ -1611,7 +1655,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="11"/>
     </row>
-    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="9">
         <v>9</v>
       </c>
@@ -1634,7 +1678,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="11"/>
     </row>
-    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -1657,7 +1701,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="11"/>
     </row>
-    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9">
         <v>11</v>
       </c>
@@ -1680,7 +1724,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="11"/>
     </row>
-    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9">
         <v>12</v>
       </c>
@@ -1703,7 +1747,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="11"/>
     </row>
-    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9">
         <v>13</v>
       </c>
@@ -1726,7 +1770,7 @@
       <c r="S23" s="10"/>
       <c r="T23" s="11"/>
     </row>
-    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9">
         <v>14</v>
       </c>
@@ -1749,7 +1793,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="11"/>
     </row>
-    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9">
         <v>15</v>
       </c>
@@ -1772,7 +1816,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="11"/>
     </row>
-    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9">
         <v>16</v>
       </c>
@@ -1795,7 +1839,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="11"/>
     </row>
-    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9">
         <v>17</v>
       </c>
@@ -1818,7 +1862,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="11"/>
     </row>
-    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="9">
         <v>18</v>
       </c>
@@ -1841,7 +1885,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="11"/>
     </row>
-    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="9">
         <v>19</v>
       </c>
@@ -1864,7 +1908,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="11"/>
     </row>
-    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9">
         <v>20</v>
       </c>
@@ -1887,7 +1931,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="11"/>
     </row>
-    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="9">
         <v>21</v>
       </c>
@@ -1910,7 +1954,7 @@
       <c r="S31" s="10"/>
       <c r="T31" s="11"/>
     </row>
-    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="9">
         <v>22</v>
       </c>
@@ -1933,7 +1977,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="11"/>
     </row>
-    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="9">
         <v>23</v>
       </c>
@@ -1956,7 +2000,7 @@
       <c r="S33" s="10"/>
       <c r="T33" s="11"/>
     </row>
-    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="9">
         <v>24</v>
       </c>
@@ -1979,7 +2023,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="11"/>
     </row>
-    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="9">
         <v>25</v>
       </c>
@@ -2002,7 +2046,7 @@
       <c r="S35" s="10"/>
       <c r="T35" s="11"/>
     </row>
-    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="9">
         <v>26</v>
       </c>
@@ -2025,7 +2069,7 @@
       <c r="S36" s="10"/>
       <c r="T36" s="11"/>
     </row>
-    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="9">
         <v>27</v>
       </c>
@@ -2048,7 +2092,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="11"/>
     </row>
-    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="9">
         <v>28</v>
       </c>
@@ -2071,7 +2115,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="11"/>
     </row>
-    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="9">
         <v>29</v>
       </c>
@@ -2094,7 +2138,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="11"/>
     </row>
-    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="9">
         <v>30</v>
       </c>
@@ -2117,7 +2161,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="11"/>
     </row>
-    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="9">
         <v>31</v>
       </c>
@@ -2140,7 +2184,7 @@
       <c r="S41" s="10"/>
       <c r="T41" s="11"/>
     </row>
-    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="9">
         <v>32</v>
       </c>
@@ -2163,7 +2207,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="9">
         <v>33</v>
       </c>
@@ -2186,7 +2230,7 @@
       <c r="S43" s="10"/>
       <c r="T43" s="11"/>
     </row>
-    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="9">
         <v>34</v>
       </c>
@@ -2209,7 +2253,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="11"/>
     </row>
-    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="9">
         <v>35</v>
       </c>
@@ -2232,7 +2276,7 @@
       <c r="S45" s="10"/>
       <c r="T45" s="11"/>
     </row>
-    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="9">
         <v>36</v>
       </c>
@@ -2255,7 +2299,7 @@
       <c r="S46" s="10"/>
       <c r="T46" s="11"/>
     </row>
-    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="9">
         <v>37</v>
       </c>
@@ -2278,7 +2322,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="11"/>
     </row>
-    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="9">
         <v>38</v>
       </c>
@@ -2301,7 +2345,7 @@
       <c r="S48" s="10"/>
       <c r="T48" s="11"/>
     </row>
-    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="9">
         <v>39</v>
       </c>
@@ -2324,7 +2368,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="11"/>
     </row>
-    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="12">
         <v>40</v>
       </c>
@@ -2347,7 +2391,7 @@
       <c r="S50" s="13"/>
       <c r="T50" s="14"/>
     </row>
-    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2362,6 +2406,11 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="T12" r:id="rId1" xr:uid="{B7426A2A-0054-44A5-A721-38719264DFEF}"/>
+    <hyperlink ref="T11" r:id="rId2" xr:uid="{B1565193-4037-44CA-B0A5-761346ECF7BE}"/>
+    <hyperlink ref="T13" r:id="rId3" xr:uid="{F34C7040-3E06-40B5-8A63-497BA2148E05}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koenm\Documents\repositorys\year_2\fae2-nlpr-group-group-4-1\fae2-nlpr-group-group-4-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0031BAB0-E3DF-4D0F-953F-CE7D9FD4ADD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61867D7-746F-4278-BF7F-0FB329A74C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15180" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="88">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -249,12 +262,6 @@
     <t>dropout=0.5, max_vocab_size=5000, Max_len = 128, batch_size=32, learning_rate 1e-3</t>
   </si>
   <si>
-    <t>Quick training</t>
-  </si>
-  <si>
-    <t>Bad inference and results</t>
-  </si>
-  <si>
     <t>Nick Belterman</t>
   </si>
   <si>
@@ -294,9 +301,6 @@
     <t>Fast to train, interpretable, and predicts across all classes instead of collapsing to only the majority ones. Performs better than Naive Bayes in terms of weighted precision/recall.</t>
   </si>
   <si>
-    <t>Still struggles on minority classes like disgust and fear. Accuracy is only 0.45 on the real client-style test set. Needs a lot of iterations to converge and still raises "did not converge" warnings in sklearn.</t>
-  </si>
-  <si>
     <t>Used class_weight='balanced' to fight label imbalance. Feature space is purely lexical (no context, no syntax).</t>
   </si>
   <si>
@@ -307,6 +311,33 @@
   </si>
   <si>
     <t xml:space="preserve">you can add more rows to the table if needed </t>
+  </si>
+  <si>
+    <t>Can capture context forward and backwards, Its simple architecture leads to quick training time, the model can also use additional features</t>
+  </si>
+  <si>
+    <t>has bigger potential to learn hierachical representations, slighty better inference result</t>
+  </si>
+  <si>
+    <t>Bad inference and results trained on small dataset, TF-IDF features may conflict with sequential LSTM modeling</t>
+  </si>
+  <si>
+    <t>Bad inference and results, trained on small dataset, TF-IDF features may conflict with sequential LSTM modeling</t>
+  </si>
+  <si>
+    <t>Normalization can stabilize training</t>
+  </si>
+  <si>
+    <t>LSTM still struggles with TF-IDF features; sequential patterns not captured.</t>
+  </si>
+  <si>
+    <t>Performance improvement minimal which suggests model architecture is not main bottleneck, trained on small dataset,</t>
+  </si>
+  <si>
+    <t>RNNs have vanishing gradient issues, not good enough accuracy, trained on small dataset,</t>
+  </si>
+  <si>
+    <t>Slightly better performance than Bi-LSTM variants, Simple model architecture generally performs better on small datasets</t>
   </si>
 </sst>
 </file>
@@ -1099,33 +1130,33 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:21" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:21" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1147,7 +1178,7 @@
       <c r="T2" s="7"/>
       <c r="U2" s="8"/>
     </row>
-    <row r="3" spans="2:21" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:21" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1202,7 @@
       <c r="T3" s="39"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="2:21" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:21" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -1192,7 +1223,7 @@
       <c r="S4" s="10"/>
       <c r="T4" s="12"/>
     </row>
-    <row r="5" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="9"/>
       <c r="C5" s="13" t="s">
         <v>1</v>
@@ -1215,7 +1246,7 @@
       <c r="S5" s="13"/>
       <c r="T5" s="15"/>
     </row>
-    <row r="6" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
       <c r="C6" s="13" t="s">
         <v>2</v>
@@ -1238,7 +1269,7 @@
       <c r="S6" s="13"/>
       <c r="T6" s="15"/>
     </row>
-    <row r="7" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -1259,7 +1290,7 @@
       <c r="S7" s="13"/>
       <c r="T7" s="15"/>
     </row>
-    <row r="8" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="9"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -1280,7 +1311,7 @@
       <c r="S8" s="13"/>
       <c r="T8" s="15"/>
     </row>
-    <row r="9" spans="2:21" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16"/>
       <c r="C9" s="42" t="s">
         <v>3</v>
@@ -1315,7 +1346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:21" s="1" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" s="1" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
         <v>10</v>
       </c>
@@ -1374,7 +1405,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="2:21" s="1" customFormat="1" ht="369.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" s="1" customFormat="1" ht="369.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="25">
         <v>1</v>
       </c>
@@ -1427,7 +1458,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="25">
         <v>2</v>
       </c>
@@ -1480,7 +1511,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:21" s="1" customFormat="1" ht="396" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" s="1" customFormat="1" ht="396" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="25">
         <v>3</v>
       </c>
@@ -1535,7 +1566,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="25">
         <v>4</v>
       </c>
@@ -1577,23 +1608,23 @@
       </c>
       <c r="O14" s="26"/>
       <c r="P14" s="26" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="26" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="R14" s="26"/>
       <c r="S14" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T14" s="30"/>
     </row>
-    <row r="15" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="25">
         <v>5</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>56</v>
@@ -1628,28 +1659,30 @@
       </c>
       <c r="O15" s="26"/>
       <c r="P15" s="26" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="Q15" s="26" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="R15" s="26"/>
       <c r="S15" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T15" s="30"/>
     </row>
-    <row r="16" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="25">
         <v>6</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="26"/>
+        <v>63</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>56</v>
+      </c>
       <c r="E16" s="26"/>
       <c r="F16" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>59</v>
@@ -1677,30 +1710,30 @@
       </c>
       <c r="O16" s="26"/>
       <c r="P16" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q16" s="26" t="s">
-        <v>63</v>
+        <v>83</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>85</v>
       </c>
       <c r="R16" s="26"/>
       <c r="S16" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T16" s="30"/>
     </row>
-    <row r="17" spans="2:20" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="25">
         <v>7</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>59</v>
@@ -1727,41 +1760,45 @@
         <v>0.45</v>
       </c>
       <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
+      <c r="P17" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>86</v>
+      </c>
       <c r="R17" s="26"/>
       <c r="S17" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T17" s="30"/>
     </row>
-    <row r="18" spans="2:20" s="1" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" s="1" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="25">
         <v>8</v>
       </c>
       <c r="C18" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="F18" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="G18" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="H18" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>73</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>34</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K18" s="29">
         <v>0.45</v>
@@ -1776,25 +1813,25 @@
         <v>0.46</v>
       </c>
       <c r="O18" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="P18" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>84</v>
+      </c>
+      <c r="R18" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="P18" s="26" t="s">
+      <c r="S18" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="Q18" s="26" t="s">
+      <c r="T18" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="R18" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="S18" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="T18" s="30" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="25">
         <v>9</v>
       </c>
@@ -1817,7 +1854,7 @@
       <c r="S19" s="26"/>
       <c r="T19" s="30"/>
     </row>
-    <row r="20" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="25">
         <v>10</v>
       </c>
@@ -1840,7 +1877,7 @@
       <c r="S20" s="26"/>
       <c r="T20" s="30"/>
     </row>
-    <row r="21" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="25">
         <v>11</v>
       </c>
@@ -1863,7 +1900,7 @@
       <c r="S21" s="26"/>
       <c r="T21" s="30"/>
     </row>
-    <row r="22" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="25">
         <v>12</v>
       </c>
@@ -1886,7 +1923,7 @@
       <c r="S22" s="26"/>
       <c r="T22" s="30"/>
     </row>
-    <row r="23" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="25">
         <v>13</v>
       </c>
@@ -1909,7 +1946,7 @@
       <c r="S23" s="26"/>
       <c r="T23" s="30"/>
     </row>
-    <row r="24" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="25">
         <v>14</v>
       </c>
@@ -1932,7 +1969,7 @@
       <c r="S24" s="26"/>
       <c r="T24" s="30"/>
     </row>
-    <row r="25" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="25">
         <v>15</v>
       </c>
@@ -1955,7 +1992,7 @@
       <c r="S25" s="26"/>
       <c r="T25" s="30"/>
     </row>
-    <row r="26" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="25">
         <v>16</v>
       </c>
@@ -1978,7 +2015,7 @@
       <c r="S26" s="26"/>
       <c r="T26" s="30"/>
     </row>
-    <row r="27" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="25">
         <v>17</v>
       </c>
@@ -2001,7 +2038,7 @@
       <c r="S27" s="26"/>
       <c r="T27" s="30"/>
     </row>
-    <row r="28" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="25">
         <v>18</v>
       </c>
@@ -2024,7 +2061,7 @@
       <c r="S28" s="26"/>
       <c r="T28" s="30"/>
     </row>
-    <row r="29" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="25">
         <v>19</v>
       </c>
@@ -2047,7 +2084,7 @@
       <c r="S29" s="26"/>
       <c r="T29" s="30"/>
     </row>
-    <row r="30" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="25">
         <v>20</v>
       </c>
@@ -2070,7 +2107,7 @@
       <c r="S30" s="26"/>
       <c r="T30" s="30"/>
     </row>
-    <row r="31" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="25">
         <v>21</v>
       </c>
@@ -2093,7 +2130,7 @@
       <c r="S31" s="26"/>
       <c r="T31" s="30"/>
     </row>
-    <row r="32" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="25">
         <v>22</v>
       </c>
@@ -2116,7 +2153,7 @@
       <c r="S32" s="26"/>
       <c r="T32" s="30"/>
     </row>
-    <row r="33" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="25">
         <v>23</v>
       </c>
@@ -2139,7 +2176,7 @@
       <c r="S33" s="26"/>
       <c r="T33" s="30"/>
     </row>
-    <row r="34" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="25">
         <v>24</v>
       </c>
@@ -2162,7 +2199,7 @@
       <c r="S34" s="26"/>
       <c r="T34" s="30"/>
     </row>
-    <row r="35" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="25">
         <v>25</v>
       </c>
@@ -2185,7 +2222,7 @@
       <c r="S35" s="26"/>
       <c r="T35" s="30"/>
     </row>
-    <row r="36" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="25">
         <v>26</v>
       </c>
@@ -2208,7 +2245,7 @@
       <c r="S36" s="26"/>
       <c r="T36" s="30"/>
     </row>
-    <row r="37" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="25">
         <v>27</v>
       </c>
@@ -2231,7 +2268,7 @@
       <c r="S37" s="26"/>
       <c r="T37" s="30"/>
     </row>
-    <row r="38" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="25">
         <v>28</v>
       </c>
@@ -2254,7 +2291,7 @@
       <c r="S38" s="26"/>
       <c r="T38" s="30"/>
     </row>
-    <row r="39" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="25">
         <v>29</v>
       </c>
@@ -2277,7 +2314,7 @@
       <c r="S39" s="26"/>
       <c r="T39" s="30"/>
     </row>
-    <row r="40" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="25">
         <v>30</v>
       </c>
@@ -2300,7 +2337,7 @@
       <c r="S40" s="26"/>
       <c r="T40" s="30"/>
     </row>
-    <row r="41" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="25">
         <v>31</v>
       </c>
@@ -2323,7 +2360,7 @@
       <c r="S41" s="26"/>
       <c r="T41" s="30"/>
     </row>
-    <row r="42" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="25">
         <v>32</v>
       </c>
@@ -2346,7 +2383,7 @@
       <c r="S42" s="26"/>
       <c r="T42" s="30"/>
     </row>
-    <row r="43" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="25">
         <v>33</v>
       </c>
@@ -2369,7 +2406,7 @@
       <c r="S43" s="26"/>
       <c r="T43" s="30"/>
     </row>
-    <row r="44" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="25">
         <v>34</v>
       </c>
@@ -2392,7 +2429,7 @@
       <c r="S44" s="26"/>
       <c r="T44" s="30"/>
     </row>
-    <row r="45" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="25">
         <v>35</v>
       </c>
@@ -2415,7 +2452,7 @@
       <c r="S45" s="26"/>
       <c r="T45" s="30"/>
     </row>
-    <row r="46" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="25">
         <v>36</v>
       </c>
@@ -2438,7 +2475,7 @@
       <c r="S46" s="26"/>
       <c r="T46" s="30"/>
     </row>
-    <row r="47" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="25">
         <v>37</v>
       </c>
@@ -2461,7 +2498,7 @@
       <c r="S47" s="26"/>
       <c r="T47" s="30"/>
     </row>
-    <row r="48" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="25">
         <v>38</v>
       </c>
@@ -2484,7 +2521,7 @@
       <c r="S48" s="26"/>
       <c r="T48" s="30"/>
     </row>
-    <row r="49" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="25">
         <v>39</v>
       </c>
@@ -2507,7 +2544,7 @@
       <c r="S49" s="26"/>
       <c r="T49" s="30"/>
     </row>
-    <row r="50" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:20" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="31">
         <v>40</v>
       </c>
@@ -2530,9 +2567,9 @@
       <c r="S50" s="32"/>
       <c r="T50" s="34"/>
     </row>
-    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61867D7-746F-4278-BF7F-0FB329A74C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B0C034-229D-44E8-83F0-DDF65E21E6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="91">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -338,6 +338,15 @@
   </si>
   <si>
     <t>Slightly better performance than Bi-LSTM variants, Simple model architecture generally performs better on small datasets</t>
+  </si>
+  <si>
+    <t>https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/blob/main/nlp_cia/src/RNN.py</t>
+  </si>
+  <si>
+    <t>https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/blob/main/nlp_cia/src/multivariate_lstm.py</t>
+  </si>
+  <si>
+    <t>Lost the file</t>
   </si>
 </sst>
 </file>
@@ -1617,7 +1626,9 @@
       <c r="S14" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="T14" s="30"/>
+      <c r="T14" s="30" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="15" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="25">
@@ -1668,7 +1679,9 @@
       <c r="S15" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="T15" s="30"/>
+      <c r="T15" s="30" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="16" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="25">
@@ -1719,7 +1732,9 @@
       <c r="S16" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="T16" s="30"/>
+      <c r="T16" s="30" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="17" spans="2:20" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="25">
@@ -1770,7 +1785,9 @@
       <c r="S17" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="T17" s="30"/>
+      <c r="T17" s="30" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="18" spans="2:20" s="1" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="25">

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B0C034-229D-44E8-83F0-DDF65E21E6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FD10DA-E18D-4EFC-B2A7-160DE0F6319C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -262,9 +262,6 @@
     <t>dropout=0.5, max_vocab_size=5000, Max_len = 128, batch_size=32, learning_rate 1e-3</t>
   </si>
   <si>
-    <t>Nick Belterman</t>
-  </si>
-  <si>
     <t>Stacked bidirectional LSTM</t>
   </si>
   <si>
@@ -347,6 +344,9 @@
   </si>
   <si>
     <t>Lost the file</t>
+  </si>
+  <si>
+    <t>Floris Lokhorst &amp; Nick Belterman</t>
   </si>
 </sst>
 </file>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="O14" s="26"/>
       <c r="P14" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q14" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R14" s="26"/>
       <c r="S14" s="26" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="T14" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>56</v>
@@ -1670,17 +1670,17 @@
       </c>
       <c r="O15" s="26"/>
       <c r="P15" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R15" s="26"/>
       <c r="S15" s="26" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="T15" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1688,14 +1688,14 @@
         <v>6</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>59</v>
@@ -1723,17 +1723,17 @@
       </c>
       <c r="O16" s="26"/>
       <c r="P16" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R16" s="26"/>
       <c r="S16" s="26" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:20" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1741,14 +1741,14 @@
         <v>7</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>59</v>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="O17" s="26"/>
       <c r="P17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R17" s="26"/>
       <c r="S17" s="26" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="T17" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:20" s="1" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1794,28 +1794,28 @@
         <v>8</v>
       </c>
       <c r="C18" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="E18" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="F18" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="G18" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="H18" s="26" t="s">
         <v>70</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>71</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>34</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18" s="29">
         <v>0.45</v>
@@ -1830,22 +1830,22 @@
         <v>0.46</v>
       </c>
       <c r="O18" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="P18" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="P18" s="26" t="s">
+      <c r="Q18" t="s">
+        <v>83</v>
+      </c>
+      <c r="R18" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="Q18" t="s">
-        <v>84</v>
-      </c>
-      <c r="R18" s="26" t="s">
+      <c r="S18" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="S18" s="26" t="s">
+      <c r="T18" s="30" t="s">
         <v>76</v>
-      </c>
-      <c r="T18" s="30" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:20" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2586,7 +2586,7 @@
     </row>
     <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Y2A_model_iteration_log.xlsx
+++ b/Y2A_model_iteration_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\fae2-nlpr-group-group-4-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickb\OneDrive\Documenten\GitHub\fae2-nlpr-group-group-4-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FD10DA-E18D-4EFC-B2A7-160DE0F6319C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FBA187-A9AE-47F8-B723-BA1EB94D70C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3660" yWindow="-20820" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -343,17 +343,20 @@
     <t>https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/blob/main/nlp_cia/src/multivariate_lstm.py</t>
   </si>
   <si>
-    <t>Lost the file</t>
-  </si>
-  <si>
     <t>Floris Lokhorst &amp; Nick Belterman</t>
+  </si>
+  <si>
+    <t>Go emotion dutch</t>
+  </si>
+  <si>
+    <t>https://github.com/BredaUniversityADSAI/fae2-nlpr-group-group-4-1/commit/860efa7fef7b5e0a578c1974baff6b8ddb7fe317</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,6 +425,14 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -696,10 +707,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -833,8 +845,12 @@
     <xf numFmtId="4" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1624,10 +1640,10 @@
       </c>
       <c r="R14" s="26"/>
       <c r="S14" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="T14" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="T14" s="45" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1640,7 +1656,9 @@
       <c r="D15" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="26"/>
+      <c r="E15" s="26" t="s">
+        <v>90</v>
+      </c>
       <c r="F15" s="26" t="s">
         <v>58</v>
       </c>
@@ -1677,10 +1695,10 @@
       </c>
       <c r="R15" s="26"/>
       <c r="S15" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T15" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="2:21" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1693,7 +1711,9 @@
       <c r="D16" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="26" t="s">
+        <v>90</v>
+      </c>
       <c r="F16" s="26" t="s">
         <v>63</v>
       </c>
@@ -1730,10 +1750,10 @@
       </c>
       <c r="R16" s="26"/>
       <c r="S16" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="2:20" s="1" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1783,7 +1803,7 @@
       </c>
       <c r="R17" s="26"/>
       <c r="S17" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T17" s="30" t="s">
         <v>87</v>
@@ -2599,6 +2619,9 @@
     <mergeCell ref="K9:O9"/>
     <mergeCell ref="P9:R9"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="T14" r:id="rId1" xr:uid="{3390221D-EC73-4E11-BD38-91BB72E61BC3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>